--- a/pds_admin_karnataka/Backend/Backend/Result_Sheet.xlsx
+++ b/pds_admin_karnataka/Backend/Backend/Result_Sheet.xlsx
@@ -103,28 +103,34 @@
     <t>FPS</t>
   </si>
   <si>
+    <t>FPS1</t>
+  </si>
+  <si>
     <t>FPS2</t>
   </si>
   <si>
     <t>FPS4</t>
   </si>
   <si>
+    <t>FPS5</t>
+  </si>
+  <si>
+    <t>FPS6</t>
+  </si>
+  <si>
+    <t>FPS7</t>
+  </si>
+  <si>
     <t>FPS8</t>
   </si>
   <si>
-    <t>FPS5</t>
-  </si>
-  <si>
     <t>FPS9</t>
   </si>
   <si>
-    <t>FPS1</t>
-  </si>
-  <si>
-    <t>FPS6</t>
-  </si>
-  <si>
-    <t>FPS7</t>
+    <t>Yavatmal Yass</t>
+  </si>
+  <si>
+    <t>Gram Mandal Maninagar</t>
   </si>
   <si>
     <t>MAHAKUTESHWAR YUVAKA MANDAL YANKANCHI</t>
@@ -133,34 +139,28 @@
     <t>L.B. NAIKAR. KHANAPUR.S.K. 68 (C)(RADDERTIMMAPUR)</t>
   </si>
   <si>
+    <t>YUVAKA MANDAL HAVALAKOD</t>
+  </si>
+  <si>
+    <t>MARUTI YUVAKA MANDAL FAKIRBUDIHAL</t>
+  </si>
+  <si>
+    <t>YUVAKA MANDAL SAGANUR</t>
+  </si>
+  <si>
     <t>YUVAKA MANDAL CHINCHALAKATTI</t>
   </si>
   <si>
-    <t>YUVAKA MANDAL HAVALAKOD</t>
-  </si>
-  <si>
     <t>K.K.LAMANI CHINCHALAKATTI L.T.</t>
   </si>
   <si>
-    <t>Yavatmal Yass</t>
-  </si>
-  <si>
-    <t>Gram Mandal Maninagar</t>
-  </si>
-  <si>
-    <t>MARUTI YUVAKA MANDAL FAKIRBUDIHAL</t>
-  </si>
-  <si>
-    <t>YUVAKA MANDAL SAGANUR</t>
-  </si>
-  <si>
     <t>FRice</t>
   </si>
   <si>
     <t>Rice</t>
   </si>
   <si>
-    <t>Millets</t>
+    <t>Ragi</t>
   </si>
   <si>
     <t>Jowar</t>
@@ -617,8 +617,8 @@
       <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
+      <c r="K2">
+        <v>4</v>
       </c>
       <c r="L2" t="s">
         <v>37</v>
@@ -633,7 +633,7 @@
         <v>24</v>
       </c>
       <c r="P2">
-        <v>16.0227</v>
+        <v>16.0238</v>
       </c>
       <c r="Q2">
         <v>75.6052</v>
@@ -642,10 +642,10 @@
         <v>46</v>
       </c>
       <c r="S2">
-        <v>75.34</v>
+        <v>677</v>
       </c>
       <c r="T2">
-        <v>1691.1721</v>
+        <v>1691.2111</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -680,7 +680,7 @@
         <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
         <v>38</v>
@@ -695,19 +695,19 @@
         <v>24</v>
       </c>
       <c r="P3">
-        <v>15.9938</v>
+        <v>16.0238</v>
       </c>
       <c r="Q3">
-        <v>75.452</v>
+        <v>75.6052</v>
       </c>
       <c r="R3" t="s">
         <v>46</v>
       </c>
       <c r="S3">
-        <v>110.89</v>
+        <v>46.46</v>
       </c>
       <c r="T3">
-        <v>1697.5976</v>
+        <v>1691.2111</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s">
         <v>39</v>
@@ -757,19 +757,19 @@
         <v>24</v>
       </c>
       <c r="P4">
-        <v>16.023</v>
+        <v>16.0227</v>
       </c>
       <c r="Q4">
-        <v>75.4657</v>
+        <v>75.6052</v>
       </c>
       <c r="R4" t="s">
         <v>46</v>
       </c>
       <c r="S4">
-        <v>58.13</v>
+        <v>75.34</v>
       </c>
       <c r="T4">
-        <v>1694.0386</v>
+        <v>1691.1721</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -786,13 +786,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>260017370006</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5">
         <v>27.89</v>
@@ -804,7 +804,7 @@
         <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
         <v>40</v>
@@ -819,19 +819,19 @@
         <v>24</v>
       </c>
       <c r="P5">
-        <v>16.0257</v>
+        <v>15.9938</v>
       </c>
       <c r="Q5">
-        <v>75.45229999999999</v>
+        <v>75.452</v>
       </c>
       <c r="R5" t="s">
         <v>46</v>
       </c>
       <c r="S5">
-        <v>55.51</v>
+        <v>110.89</v>
       </c>
       <c r="T5">
-        <v>1697.0919</v>
+        <v>1697.5976</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -866,7 +866,7 @@
         <v>28</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
         <v>41</v>
@@ -881,19 +881,19 @@
         <v>24</v>
       </c>
       <c r="P6">
-        <v>16.0242</v>
+        <v>16.0257</v>
       </c>
       <c r="Q6">
-        <v>75.4815</v>
+        <v>75.45229999999999</v>
       </c>
       <c r="R6" t="s">
         <v>46</v>
       </c>
       <c r="S6">
-        <v>38.08</v>
+        <v>55.51</v>
       </c>
       <c r="T6">
-        <v>1692.1932</v>
+        <v>1697.0919</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -910,10 +910,10 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>
@@ -927,8 +927,8 @@
       <c r="J7" t="s">
         <v>28</v>
       </c>
-      <c r="K7">
-        <v>4</v>
+      <c r="K7" t="s">
+        <v>33</v>
       </c>
       <c r="L7" t="s">
         <v>42</v>
@@ -943,19 +943,19 @@
         <v>24</v>
       </c>
       <c r="P7">
-        <v>16.0238</v>
+        <v>16.0502</v>
       </c>
       <c r="Q7">
-        <v>75.6052</v>
+        <v>75.47539999999999</v>
       </c>
       <c r="R7" t="s">
         <v>46</v>
       </c>
       <c r="S7">
-        <v>677</v>
+        <v>37.54</v>
       </c>
       <c r="T7">
-        <v>1691.2111</v>
+        <v>1697.2908</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -972,10 +972,10 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G8" t="s">
         <v>27</v>
@@ -1005,19 +1005,19 @@
         <v>24</v>
       </c>
       <c r="P8">
-        <v>16.0238</v>
+        <v>16.0437</v>
       </c>
       <c r="Q8">
-        <v>75.6052</v>
+        <v>75.474</v>
       </c>
       <c r="R8" t="s">
         <v>46</v>
       </c>
       <c r="S8">
-        <v>46.46</v>
+        <v>27.24</v>
       </c>
       <c r="T8">
-        <v>1691.2111</v>
+        <v>1696.592</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1034,10 +1034,10 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -1067,19 +1067,19 @@
         <v>24</v>
       </c>
       <c r="P9">
-        <v>16.0502</v>
+        <v>16.023</v>
       </c>
       <c r="Q9">
-        <v>75.47539999999999</v>
+        <v>75.4657</v>
       </c>
       <c r="R9" t="s">
         <v>46</v>
       </c>
       <c r="S9">
-        <v>37.54</v>
+        <v>58.13</v>
       </c>
       <c r="T9">
-        <v>1697.2908</v>
+        <v>1694.0386</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1096,10 +1096,10 @@
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>26001737000</v>
+        <v>260017370006</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
@@ -1129,19 +1129,19 @@
         <v>24</v>
       </c>
       <c r="P10">
-        <v>16.0437</v>
+        <v>16.0242</v>
       </c>
       <c r="Q10">
-        <v>75.474</v>
+        <v>75.4815</v>
       </c>
       <c r="R10" t="s">
         <v>46</v>
       </c>
       <c r="S10">
-        <v>27.24</v>
+        <v>38.08</v>
       </c>
       <c r="T10">
-        <v>1696.592</v>
+        <v>1692.1932</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1161,10 +1161,10 @@
         <v>24</v>
       </c>
       <c r="F11">
-        <v>26001737000</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11">
         <v>27.89</v>
@@ -1179,7 +1179,7 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
         <v>22</v>
@@ -1241,7 +1241,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M12" t="s">
         <v>22</v>
@@ -1300,10 +1300,10 @@
         <v>28</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M13" t="s">
         <v>22</v>
@@ -1362,10 +1362,10 @@
         <v>28</v>
       </c>
       <c r="K14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" t="s">
         <v>22</v>
@@ -1424,10 +1424,10 @@
         <v>28</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M15" t="s">
         <v>22</v>
@@ -1489,7 +1489,7 @@
         <v>32</v>
       </c>
       <c r="L16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M16" t="s">
         <v>22</v>
@@ -1548,10 +1548,10 @@
         <v>28</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M17" t="s">
         <v>22</v>
@@ -1610,10 +1610,10 @@
         <v>28</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M18" t="s">
         <v>22</v>
@@ -1672,10 +1672,10 @@
         <v>28</v>
       </c>
       <c r="K19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L19" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M19" t="s">
         <v>22</v>
@@ -1734,10 +1734,10 @@
         <v>28</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L20" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M20" t="s">
         <v>22</v>
@@ -1799,7 +1799,7 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M21" t="s">
         <v>22</v>
@@ -1858,10 +1858,10 @@
         <v>28</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M22" t="s">
         <v>22</v>
@@ -1920,10 +1920,10 @@
         <v>28</v>
       </c>
       <c r="K23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M23" t="s">
         <v>22</v>
@@ -1982,10 +1982,10 @@
         <v>28</v>
       </c>
       <c r="K24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L24" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M24" t="s">
         <v>22</v>
@@ -2047,7 +2047,7 @@
         <v>32</v>
       </c>
       <c r="L25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M25" t="s">
         <v>22</v>
@@ -2106,10 +2106,10 @@
         <v>28</v>
       </c>
       <c r="K26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M26" t="s">
         <v>22</v>
@@ -2168,10 +2168,10 @@
         <v>28</v>
       </c>
       <c r="K27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L27" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M27" t="s">
         <v>22</v>
@@ -2230,10 +2230,10 @@
         <v>28</v>
       </c>
       <c r="K28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L28" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M28" t="s">
         <v>22</v>
@@ -2292,10 +2292,10 @@
         <v>28</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L29" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M29" t="s">
         <v>22</v>
